--- a/data/trans_camb/P11_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P11_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 3,88</t>
+          <t>-10,91; 3,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 4,44</t>
+          <t>-11,02; 3,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 13,02</t>
+          <t>-3,08; 12,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 10,39</t>
+          <t>-7,53; 10,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 11,44</t>
+          <t>-5,03; 11,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 22,49</t>
+          <t>7,56; 22,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 4,54</t>
+          <t>-6,57; 4,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 5,23</t>
+          <t>-6,12; 4,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 15,47</t>
+          <t>4,57; 16,18</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 19,13</t>
+          <t>-39,36; 17,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 23,31</t>
+          <t>-40,1; 17,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 62,09</t>
+          <t>-11,93; 64,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 33,46</t>
+          <t>-18,13; 33,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 36,43</t>
+          <t>-13,32; 39,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,93; 75,5</t>
+          <t>18,74; 74,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 17,43</t>
+          <t>-20,17; 16,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 20,1</t>
+          <t>-19,2; 17,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,76; 59,12</t>
+          <t>14,0; 59,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,59; -2,62</t>
+          <t>-12,67; -2,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,54; -3,67</t>
+          <t>-13,38; -3,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 7,27</t>
+          <t>-4,81; 7,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,52; -6,6</t>
+          <t>-18,64; -6,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,0; -14,31</t>
+          <t>-25,69; -13,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,02; -1,67</t>
+          <t>-12,36; -1,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,49; -6,46</t>
+          <t>-14,2; -6,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -10,54</t>
+          <t>-18,49; -10,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 1,35</t>
+          <t>-7,36; 1,01</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,51; -13,19</t>
+          <t>-51,16; -11,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,38; -19,93</t>
+          <t>-55,29; -20,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 38,06</t>
+          <t>-19,07; 36,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,69; -17,29</t>
+          <t>-41,65; -16,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,63; -36,85</t>
+          <t>-58,06; -36,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,83; -4,01</t>
+          <t>-27,97; -4,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,45; -21,73</t>
+          <t>-41,29; -19,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,74; -34,82</t>
+          <t>-54,11; -35,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-21,03; 4,66</t>
+          <t>-21,44; 3,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 8,75</t>
+          <t>-2,44; 8,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 5,86</t>
+          <t>-5,05; 4,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,62; 25,8</t>
+          <t>13,33; 25,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 6,3</t>
+          <t>-7,14; 6,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 2,8</t>
+          <t>-10,69; 2,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 15,84</t>
+          <t>3,5; 15,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 5,5</t>
+          <t>-2,83; 5,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 2,39</t>
+          <t>-6,5; 2,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,86; 18,89</t>
+          <t>10,31; 19,25</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 82,4</t>
+          <t>-17,85; 83,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,16; 57,99</t>
+          <t>-32,47; 47,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83,3; 248,17</t>
+          <t>80,71; 241,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 26,93</t>
+          <t>-23,61; 28,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 12,13</t>
+          <t>-34,42; 10,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,35; 67,84</t>
+          <t>10,75; 68,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 30,27</t>
+          <t>-12,47; 32,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,46; 13,66</t>
+          <t>-28,67; 11,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43,05; 105,06</t>
+          <t>44,63; 106,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 1,22</t>
+          <t>-9,29; 2,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 7,21</t>
+          <t>-4,54; 7,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 17,9</t>
+          <t>3,23; 17,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 6,41</t>
+          <t>-6,36; 6,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 9,79</t>
+          <t>-4,28; 9,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 10,33</t>
+          <t>-14,85; 10,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 2,23</t>
+          <t>-6,65; 2,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 6,39</t>
+          <t>-2,52; 6,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 11,66</t>
+          <t>-4,0; 11,38</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 6,65</t>
+          <t>-39,85; 11,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 40,04</t>
+          <t>-20,32; 39,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,32; 97,95</t>
+          <t>13,19; 93,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 20,29</t>
+          <t>-17,06; 19,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 30,49</t>
+          <t>-11,4; 28,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,02; 31,49</t>
+          <t>-39,38; 30,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 8,83</t>
+          <t>-21,94; 10,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 25,33</t>
+          <t>-8,15; 26,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 44,1</t>
+          <t>-13,14; 43,4</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 14,43</t>
+          <t>-1,35; 14,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 14,02</t>
+          <t>-0,79; 15,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 15,48</t>
+          <t>1,26; 15,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,37; 31,72</t>
+          <t>14,49; 31,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 14,63</t>
+          <t>-1,87; 15,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,5; 18,08</t>
+          <t>2,95; 17,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,13; 21,3</t>
+          <t>8,95; 20,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 12,06</t>
+          <t>1,21; 12,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,02; 14,29</t>
+          <t>4,63; 14,59</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 126,46</t>
+          <t>-8,81; 123,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 127,45</t>
+          <t>-5,68; 133,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3,94; 134,55</t>
+          <t>3,76; 129,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49,47; 180,19</t>
+          <t>52,06; 168,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 77,88</t>
+          <t>-7,62; 81,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,44; 99,3</t>
+          <t>9,8; 95,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,58; 129,28</t>
+          <t>40,97; 124,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,82; 73,42</t>
+          <t>4,66; 76,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17,67; 87,41</t>
+          <t>20,6; 90,39</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 12,96</t>
+          <t>-1,84; 12,05</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 10,26</t>
+          <t>-3,72; 10,18</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17,14; 31,39</t>
+          <t>17,04; 31,44</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 7,48</t>
+          <t>-7,3; 7,32</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 9,34</t>
+          <t>-6,92; 8,69</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,23; 31,79</t>
+          <t>17,68; 32,43</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 8,24</t>
+          <t>-2,5; 7,21</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 8,0</t>
+          <t>-2,97; 7,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>19,58; 29,57</t>
+          <t>19,46; 29,52</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 81,05</t>
+          <t>-7,44; 78,77</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 64,73</t>
+          <t>-17,07; 63,05</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>72,13; 209,18</t>
+          <t>70,58; 197,47</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 29,44</t>
+          <t>-22,43; 29,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 36,91</t>
+          <t>-20,72; 34,0</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>49,79; 125,29</t>
+          <t>52,16; 128,65</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 38,24</t>
+          <t>-9,07; 33,95</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 35,64</t>
+          <t>-11,02; 33,72</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>71,65; 141,81</t>
+          <t>70,43; 137,31</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 5,26</t>
+          <t>-3,05; 4,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4,84; 13,57</t>
+          <t>5,03; 13,45</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7,81; 16,94</t>
+          <t>7,47; 16,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,77</t>
+          <t>1,74; 11,14</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,62; 15,25</t>
+          <t>6,02; 15,5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,99; 55,85</t>
+          <t>13,14; 56,33</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,38; 6,84</t>
+          <t>0,66; 6,9</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,52; 13,2</t>
+          <t>6,73; 13,36</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,31; 46,13</t>
+          <t>12,54; 46,58</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 42,79</t>
+          <t>-18,65; 41,18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>29,8; 112,6</t>
+          <t>31,53; 111,15</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>48,83; 137,76</t>
+          <t>48,55; 143,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,46; 56,96</t>
+          <t>8,02; 60,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>24,39; 81,49</t>
+          <t>26,07; 83,89</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>59,96; 291,07</t>
+          <t>61,23; 291,93</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,88; 43,68</t>
+          <t>3,88; 43,56</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>33,55; 83,42</t>
+          <t>36,2; 83,03</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>68,28; 266,82</t>
+          <t>70,43; 296,18</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,56</t>
+          <t>1,36; 10,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 1,54</t>
+          <t>-6,6; 1,25</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 1,11</t>
+          <t>-13,74; 1,2</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,72</t>
+          <t>0,61; 10,63</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 4,65</t>
+          <t>-4,86; 4,45</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 8,56</t>
+          <t>-0,97; 8,15</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,42</t>
+          <t>2,47; 8,89</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 1,56</t>
+          <t>-4,34; 1,56</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 2,77</t>
+          <t>-11,15; 2,75</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>5,67; 59,03</t>
+          <t>6,05; 60,59</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-29,66; 9,28</t>
+          <t>-32,22; 7,14</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-70,99; 6,37</t>
+          <t>-67,17; 7,36</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4,21; 45,57</t>
+          <t>2,21; 44,26</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 20,3</t>
+          <t>-17,25; 18,64</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 37,2</t>
+          <t>-3,43; 34,97</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,94; 45,5</t>
+          <t>10,43; 42,52</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 7,62</t>
+          <t>-18,22; 7,41</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-45,08; 12,54</t>
+          <t>-49,23; 12,65</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,72</t>
+          <t>-1,11; 2,62</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,4</t>
+          <t>-1,34; 2,31</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,42</t>
+          <t>0,97; 9,5</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,38</t>
+          <t>-0,06; 4,39</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,66</t>
+          <t>-2,61; 1,93</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,26; 22,25</t>
+          <t>6,38; 22,0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,91</t>
+          <t>0,03; 2,94</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,49</t>
+          <t>-1,37; 1,51</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,51; 15,81</t>
+          <t>5,71; 15,21</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 15,82</t>
+          <t>-5,86; 14,92</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 14,26</t>
+          <t>-7,04; 13,51</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6,22; 53,24</t>
+          <t>6,48; 55,0</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 15,5</t>
+          <t>-0,1; 15,6</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 5,84</t>
+          <t>-8,68; 6,91</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>21,23; 78,83</t>
+          <t>21,61; 76,75</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 12,62</t>
+          <t>0,27; 12,91</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 6,54</t>
+          <t>-5,58; 6,51</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>22,45; 65,63</t>
+          <t>23,19; 66,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P11_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P11_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>3,98</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,19</t>
+          <t>13,83</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>8,98</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 3,45</t>
+          <t>-11,36; 3,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 3,66</t>
+          <t>-10,7; 3,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 12,9</t>
+          <t>-3,07; 11,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 10,06</t>
+          <t>-6,66; 10,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 11,45</t>
+          <t>-5,18; 11,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 22,71</t>
+          <t>6,02; 21,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 4,49</t>
+          <t>-6,44; 5,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 4,67</t>
+          <t>-5,91; 5,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 16,18</t>
+          <t>3,88; 14,21</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 17,08</t>
+          <t>-40,31; 16,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,1; 17,37</t>
+          <t>-38,58; 17,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 64,02</t>
+          <t>-11,12; 53,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 33,56</t>
+          <t>-17,59; 35,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 39,44</t>
+          <t>-13,32; 38,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,74; 74,87</t>
+          <t>15,67; 74,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 16,8</t>
+          <t>-20,18; 19,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 17,5</t>
+          <t>-17,81; 21,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,0; 59,82</t>
+          <t>10,97; 52,88</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>2,0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,03</t>
+          <t>-7,45</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>-2,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,67; -2,49</t>
+          <t>-12,39; -2,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,38; -3,92</t>
+          <t>-13,22; -4,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 7,17</t>
+          <t>-3,35; 7,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,64; -6,24</t>
+          <t>-19,27; -6,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,69; -13,9</t>
+          <t>-25,78; -14,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,36; -1,54</t>
+          <t>-13,25; -1,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,2; -6,11</t>
+          <t>-14,03; -5,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,49; -10,61</t>
+          <t>-18,25; -10,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 1,01</t>
+          <t>-6,71; 1,19</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-16,84%</t>
+          <t>-17,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-9,15%</t>
+          <t>-8,65%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,16; -11,92</t>
+          <t>-52,06; -13,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,29; -20,46</t>
+          <t>-54,59; -20,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 36,9</t>
+          <t>-13,48; 40,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,65; -16,4</t>
+          <t>-42,85; -17,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,06; -36,13</t>
+          <t>-58,36; -36,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,97; -4,05</t>
+          <t>-29,01; -3,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,29; -19,91</t>
+          <t>-41,35; -19,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,11; -35,34</t>
+          <t>-53,9; -35,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 3,38</t>
+          <t>-20,06; 3,69</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,66</t>
+          <t>20,46</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,72</t>
+          <t>10,05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>15,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 8,7</t>
+          <t>-2,19; 8,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 4,96</t>
+          <t>-4,72; 5,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,33; 25,34</t>
+          <t>14,76; 26,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 6,69</t>
+          <t>-7,99; 6,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 2,44</t>
+          <t>-10,88; 2,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 15,85</t>
+          <t>3,62; 16,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 5,81</t>
+          <t>-3,23; 5,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 2,04</t>
+          <t>-6,28; 2,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,31; 19,25</t>
+          <t>10,83; 19,76</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151,73%</t>
+          <t>157,93%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>75,59%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 83,69</t>
+          <t>-14,96; 86,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 47,44</t>
+          <t>-29,09; 61,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80,71; 241,59</t>
+          <t>95,37; 272,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 28,64</t>
+          <t>-26,2; 25,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 10,57</t>
+          <t>-35,55; 10,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,75; 68,28</t>
+          <t>11,78; 69,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 32,68</t>
+          <t>-14,66; 32,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 11,71</t>
+          <t>-28,49; 13,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,63; 106,09</t>
+          <t>47,44; 111,43</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,23</t>
+          <t>8,66</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>8,59</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,26</t>
+          <t>8,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 2,23</t>
+          <t>-9,78; 2,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 7,17</t>
+          <t>-4,82; 7,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,23; 17,12</t>
+          <t>2,13; 16,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 6,21</t>
+          <t>-7,13; 6,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 9,41</t>
+          <t>-4,99; 9,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 10,2</t>
+          <t>1,86; 15,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 2,75</t>
+          <t>-6,45; 2,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 6,65</t>
+          <t>-2,41; 6,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 11,38</t>
+          <t>3,74; 14,28</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0,56%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 11,96</t>
+          <t>-41,7; 14,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 39,7</t>
+          <t>-20,54; 43,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,19; 93,38</t>
+          <t>8,7; 90,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 19,66</t>
+          <t>-18,18; 20,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 28,83</t>
+          <t>-13,04; 30,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 30,7</t>
+          <t>4,66; 48,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 10,99</t>
+          <t>-21,45; 10,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 26,26</t>
+          <t>-8,33; 27,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 43,4</t>
+          <t>11,53; 55,27</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,41</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,37</t>
+          <t>8,81</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,72</t>
+          <t>8,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 14,59</t>
+          <t>-1,12; 13,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 15,06</t>
+          <t>-1,25; 13,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 15,2</t>
+          <t>0,26; 13,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,49; 31,62</t>
+          <t>13,62; 31,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 15,0</t>
+          <t>-2,34; 14,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 17,89</t>
+          <t>0,72; 15,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,95; 20,29</t>
+          <t>8,99; 20,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,21; 12,66</t>
+          <t>0,26; 12,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,63; 14,59</t>
+          <t>3,18; 13,31</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 123,23</t>
+          <t>-6,31; 115,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 133,35</t>
+          <t>-8,89; 108,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3,76; 129,01</t>
+          <t>-0,35; 117,69</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52,06; 168,14</t>
+          <t>45,88; 171,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 81,75</t>
+          <t>-9,27; 79,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,8; 95,23</t>
+          <t>2,41; 86,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,97; 124,09</t>
+          <t>41,64; 130,85</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4,66; 76,35</t>
+          <t>1,54; 75,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>20,6; 90,39</t>
+          <t>13,65; 82,07</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24,54</t>
+          <t>24,55</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,96</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>24,55</t>
+          <t>24,74</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 12,05</t>
+          <t>-1,59; 13,49</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 10,18</t>
+          <t>-4,07; 9,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17,04; 31,44</t>
+          <t>17,16; 31,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 7,32</t>
+          <t>-8,73; 7,61</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 8,69</t>
+          <t>-6,97; 8,58</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,68; 32,43</t>
+          <t>17,84; 32,29</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 7,21</t>
+          <t>-2,37; 7,48</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 7,26</t>
+          <t>-3,63; 7,18</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>19,46; 29,52</t>
+          <t>19,2; 29,72</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>128,2%</t>
+          <t>128,25%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>100,57%</t>
+          <t>101,33%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 78,77</t>
+          <t>-8,32; 85,17</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 63,05</t>
+          <t>-19,65; 58,92</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>70,58; 197,47</t>
+          <t>72,55; 196,04</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 29,47</t>
+          <t>-26,08; 29,64</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 34,0</t>
+          <t>-20,36; 33,98</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>52,16; 128,65</t>
+          <t>52,67; 128,24</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 33,95</t>
+          <t>-9,08; 35,13</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 33,72</t>
+          <t>-13,29; 33,44</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70,43; 137,31</t>
+          <t>71,69; 139,81</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12,21</t>
+          <t>12,88</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,25</t>
+          <t>14,6</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>23,05</t>
+          <t>13,82</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,88</t>
+          <t>-2,8; 5,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5,03; 13,45</t>
+          <t>4,69; 13,3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7,47; 16,9</t>
+          <t>8,35; 17,56</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,74; 11,14</t>
+          <t>1,41; 11,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,02; 15,5</t>
+          <t>5,74; 15,66</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,14; 56,33</t>
+          <t>9,84; 18,52</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,9</t>
+          <t>0,6; 7,06</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,73; 13,36</t>
+          <t>6,65; 13,37</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,54; 46,58</t>
+          <t>10,81; 17,11</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>146,92%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>132,81%</t>
+          <t>79,65%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 41,18</t>
+          <t>-17,84; 42,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>31,53; 111,15</t>
+          <t>28,36; 109,19</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>48,55; 143,52</t>
+          <t>50,44; 147,32</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8,02; 60,65</t>
+          <t>6,22; 59,73</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>26,07; 83,89</t>
+          <t>24,31; 83,05</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>61,23; 291,93</t>
+          <t>41,99; 101,03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,88; 43,56</t>
+          <t>3,18; 44,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>36,2; 83,03</t>
+          <t>36,02; 84,21</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>70,43; 296,18</t>
+          <t>56,53; 109,47</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-4,97</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>1,33</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,36; 10,0</t>
+          <t>1,24; 9,74</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 1,25</t>
+          <t>-6,58; 1,27</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 1,2</t>
+          <t>-4,17; 3,82</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,61; 10,63</t>
+          <t>0,96; 10,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 4,45</t>
+          <t>-4,87; 4,13</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 8,15</t>
+          <t>-1,4; 7,09</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,47; 8,89</t>
+          <t>2,58; 9,06</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 1,56</t>
+          <t>-4,13; 1,87</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 2,75</t>
+          <t>-1,51; 4,22</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-26,95%</t>
+          <t>-1,97%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-7,84%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>6,05; 60,59</t>
+          <t>6,6; 60,78</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 7,14</t>
+          <t>-31,47; 8,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-67,17; 7,36</t>
+          <t>-20,08; 23,24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2,21; 44,26</t>
+          <t>3,5; 44,6</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 18,64</t>
+          <t>-17,41; 17,18</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 34,97</t>
+          <t>-5,05; 29,06</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,43; 42,52</t>
+          <t>11,06; 43,55</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 7,41</t>
+          <t>-17,5; 9,07</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-49,23; 12,65</t>
+          <t>-6,31; 19,81</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>8,27</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,0</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8,98</t>
+          <t>8,16</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,62</t>
+          <t>-1,23; 2,61</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,31</t>
+          <t>-1,61; 2,23</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,5</t>
+          <t>6,12; 10,19</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,39</t>
+          <t>-0,24; 4,36</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,93</t>
+          <t>-2,73; 1,7</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,38; 22,0</t>
+          <t>5,7; 9,94</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,94</t>
+          <t>-0,13; 2,85</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,51</t>
+          <t>-1,48; 1,55</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,71; 15,21</t>
+          <t>6,68; 9,73</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 14,92</t>
+          <t>-6,4; 15,18</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 13,51</t>
+          <t>-8,49; 12,95</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6,48; 55,0</t>
+          <t>31,52; 58,28</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 15,6</t>
+          <t>-0,81; 15,43</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 6,91</t>
+          <t>-9,02; 6,03</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>21,61; 76,75</t>
+          <t>18,85; 35,22</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,27; 12,91</t>
+          <t>-0,57; 12,3</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 6,51</t>
+          <t>-5,99; 6,77</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>23,19; 66,02</t>
+          <t>27,2; 42,52</t>
         </is>
       </c>
     </row>
